--- a/DÍA 4/Formulas+Matriciales.xlsx
+++ b/DÍA 4/Formulas+Matriciales.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GUSTAVO\Documents\Cursos Udemy\ExcelTotal\DÍA 4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C5C515-DBCC-4AC3-88FF-4BD9B4C4C8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC75BD5C-2ADD-400D-BA8B-69A438816AA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{4315D6B6-341C-4438-9F87-504645EF22AF}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -290,7 +290,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -309,15 +309,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
@@ -633,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE68ECC8-5C64-4FFB-AEF5-7E555BAE7BF2}">
-  <dimension ref="B1:O20"/>
+  <dimension ref="B1:P20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="2.88671875" customWidth="1"/>
@@ -644,9 +647,10 @@
     <col min="12" max="12" width="3.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="6.6640625" customWidth="1"/>
+    <col min="16" max="16" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
@@ -662,7 +666,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -678,7 +682,7 @@
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
-    <row r="3" spans="2:15" ht="31.8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" ht="31.8" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>158</v>
       </c>
@@ -698,7 +702,7 @@
       <c r="I3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="18" t="s">
         <v>12</v>
       </c>
       <c r="K3" s="1"/>
@@ -711,7 +715,7 @@
       <c r="N3" s="1"/>
       <c r="O3" s="1"/>
     </row>
-    <row r="4" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
@@ -739,8 +743,9 @@
       </c>
       <c r="N4" s="1"/>
       <c r="O4" s="1"/>
-    </row>
-    <row r="5" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P4" s="22"/>
+    </row>
+    <row r="5" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>158</v>
       </c>
@@ -773,8 +778,9 @@
       </c>
       <c r="N5" s="1"/>
       <c r="O5" s="1"/>
-    </row>
-    <row r="6" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P5" s="22"/>
+    </row>
+    <row r="6" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>300</v>
       </c>
@@ -806,8 +812,9 @@
       </c>
       <c r="N6" s="1"/>
       <c r="O6" s="1"/>
-    </row>
-    <row r="7" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P6" s="22"/>
+    </row>
+    <row r="7" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>415</v>
       </c>
@@ -839,8 +846,9 @@
       </c>
       <c r="N7" s="1"/>
       <c r="O7" s="1"/>
-    </row>
-    <row r="8" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P7" s="22"/>
+    </row>
+    <row r="8" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -862,8 +870,9 @@
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
-    </row>
-    <row r="9" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P8" s="23"/>
+    </row>
+    <row r="9" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
@@ -884,8 +893,9 @@
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
-    </row>
-    <row r="10" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P9" s="21"/>
+    </row>
+    <row r="10" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="H10" s="16" cm="1">
         <f t="array" ref="H10">SUM(H4:H7*I4:I7)</f>
         <v>166504.72999999998</v>
@@ -902,14 +912,14 @@
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
     </row>
-    <row r="11" spans="2:15" ht="21" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:16" ht="21" x14ac:dyDescent="0.4">
       <c r="G11" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="18" t="s">
+      <c r="H11" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="I11" s="18"/>
+      <c r="I11" s="20"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="11">
@@ -920,8 +930,9 @@
       </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
-    </row>
-    <row r="12" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+      <c r="P11" s="21"/>
+    </row>
+    <row r="12" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
@@ -934,7 +945,7 @@
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
     </row>
-    <row r="13" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
@@ -947,7 +958,7 @@
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
     </row>
-    <row r="14" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
@@ -963,7 +974,7 @@
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
     </row>
-    <row r="15" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B15" s="19" t="s">
         <v>11</v>
       </c>
@@ -986,7 +997,7 @@
       </c>
       <c r="O15" s="1"/>
     </row>
-    <row r="16" spans="2:15" ht="18" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
       <c r="D16" s="19"/>
